--- a/TabelaEstoque.xlsx
+++ b/TabelaEstoque.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marcel\Desktop\Nova pasta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FB6A6BA-41B2-4DAD-AD28-C49371BB9004}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC464E27-0982-4368-891A-50AF97AFE3EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F1C51C6C-6C7F-4680-B750-27F2425B38AD}"/>
   </bookViews>
   <sheets>
     <sheet name="Estoque" sheetId="1" r:id="rId1"/>
@@ -24,8 +24,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -36,9 +34,6 @@
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="13">
   <si>
     <t>Data</t>
-  </si>
-  <si>
-    <t>Produto</t>
   </si>
   <si>
     <t>Tipo</t>
@@ -62,16 +57,19 @@
     <t>Valor Total em Estoque</t>
   </si>
   <si>
-    <t>Morango</t>
+    <t>Compra</t>
   </si>
   <si>
-    <t>Compra</t>
+    <t>Venda</t>
+  </si>
+  <si>
+    <t>Produto</t>
   </si>
   <si>
     <t>Tomate</t>
   </si>
   <si>
-    <t>Venda</t>
+    <t>Morango</t>
   </si>
 </sst>
 </file>
@@ -81,7 +79,7 @@
   <numFmts count="1">
     <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -96,13 +94,312 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Aptos Display"/>
+      <family val="2"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C5700"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -111,7 +408,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -119,26 +416,215 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="33" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="16" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="16" fontId="0" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="43">
+    <cellStyle name="20% - Accent1" xfId="20" builtinId="30" customBuiltin="1"/>
+    <cellStyle name="20% - Accent2" xfId="24" builtinId="34" customBuiltin="1"/>
+    <cellStyle name="20% - Accent3" xfId="28" builtinId="38" customBuiltin="1"/>
+    <cellStyle name="20% - Accent4" xfId="32" builtinId="42" customBuiltin="1"/>
+    <cellStyle name="20% - Accent5" xfId="36" builtinId="46" customBuiltin="1"/>
+    <cellStyle name="20% - Accent6" xfId="40" builtinId="50" customBuiltin="1"/>
+    <cellStyle name="40% - Accent1" xfId="21" builtinId="31" customBuiltin="1"/>
+    <cellStyle name="40% - Accent2" xfId="25" builtinId="35" customBuiltin="1"/>
+    <cellStyle name="40% - Accent3" xfId="29" builtinId="39" customBuiltin="1"/>
+    <cellStyle name="40% - Accent4" xfId="33" builtinId="43" customBuiltin="1"/>
+    <cellStyle name="40% - Accent5" xfId="37" builtinId="47" customBuiltin="1"/>
+    <cellStyle name="40% - Accent6" xfId="41" builtinId="51" customBuiltin="1"/>
+    <cellStyle name="60% - Accent1" xfId="22" builtinId="32" customBuiltin="1"/>
+    <cellStyle name="60% - Accent2" xfId="26" builtinId="36" customBuiltin="1"/>
+    <cellStyle name="60% - Accent3" xfId="30" builtinId="40" customBuiltin="1"/>
+    <cellStyle name="60% - Accent4" xfId="34" builtinId="44" customBuiltin="1"/>
+    <cellStyle name="60% - Accent5" xfId="38" builtinId="48" customBuiltin="1"/>
+    <cellStyle name="60% - Accent6" xfId="42" builtinId="52" customBuiltin="1"/>
+    <cellStyle name="Accent1" xfId="19" builtinId="29" customBuiltin="1"/>
+    <cellStyle name="Accent2" xfId="23" builtinId="33" customBuiltin="1"/>
+    <cellStyle name="Accent3" xfId="27" builtinId="37" customBuiltin="1"/>
+    <cellStyle name="Accent4" xfId="31" builtinId="41" customBuiltin="1"/>
+    <cellStyle name="Accent5" xfId="35" builtinId="45" customBuiltin="1"/>
+    <cellStyle name="Accent6" xfId="39" builtinId="49" customBuiltin="1"/>
+    <cellStyle name="Bad" xfId="8" builtinId="27" customBuiltin="1"/>
+    <cellStyle name="Calculation" xfId="12" builtinId="22" customBuiltin="1"/>
+    <cellStyle name="Check Cell" xfId="14" builtinId="23" customBuiltin="1"/>
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
+    <cellStyle name="Explanatory Text" xfId="17" builtinId="53" customBuiltin="1"/>
+    <cellStyle name="Good" xfId="7" builtinId="26" customBuiltin="1"/>
+    <cellStyle name="Heading 1" xfId="3" builtinId="16" customBuiltin="1"/>
+    <cellStyle name="Heading 2" xfId="4" builtinId="17" customBuiltin="1"/>
+    <cellStyle name="Heading 3" xfId="5" builtinId="18" customBuiltin="1"/>
+    <cellStyle name="Heading 4" xfId="6" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="Input" xfId="10" builtinId="20" customBuiltin="1"/>
+    <cellStyle name="Linked Cell" xfId="13" builtinId="24" customBuiltin="1"/>
+    <cellStyle name="Neutral" xfId="9" builtinId="28" customBuiltin="1"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Note" xfId="16" builtinId="10" customBuiltin="1"/>
+    <cellStyle name="Output" xfId="11" builtinId="21" customBuiltin="1"/>
+    <cellStyle name="Title" xfId="2" builtinId="15" customBuiltin="1"/>
+    <cellStyle name="Total" xfId="18" builtinId="25" customBuiltin="1"/>
+    <cellStyle name="Warning Text" xfId="15" builtinId="11" customBuiltin="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -469,56 +955,55 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I31"/>
-  <sheetFormatPr defaultColWidth="22.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07444E34-007A-49FC-B429-A6B508056B29}">
+  <dimension ref="A1:I30"/>
+  <sheetFormatPr defaultColWidth="22.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="4" width="22.7109375" style="1" customWidth="1"/>
-    <col min="5" max="6" width="22.7109375" style="2" customWidth="1"/>
-    <col min="7" max="7" width="22.7109375" style="1" customWidth="1"/>
-    <col min="8" max="9" width="22.7109375" style="2" customWidth="1"/>
-    <col min="10" max="10" width="22.7109375" style="1" customWidth="1"/>
-    <col min="11" max="16384" width="22.7109375" style="1"/>
+    <col min="1" max="4" width="22.6640625" style="1"/>
+    <col min="5" max="6" width="22.6640625" style="2"/>
+    <col min="7" max="7" width="22.6640625" style="1"/>
+    <col min="8" max="9" width="22.6640625" style="2"/>
+    <col min="10" max="16384" width="22.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="3">
         <v>46082</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D2" s="1">
         <v>100</v>
@@ -527,7 +1012,7 @@
         <v>10</v>
       </c>
       <c r="F2" s="2">
-        <f t="shared" ref="F2:F30" si="0">(D2*E2)</f>
+        <f>(D2*E2)</f>
         <v>1000</v>
       </c>
       <c r="G2" s="1">
@@ -539,11 +1024,11 @@
         <v>10</v>
       </c>
       <c r="I2" s="2">
-        <f t="shared" ref="I2:I30" si="1">G2*H2</f>
+        <f>G2*H2</f>
         <v>1000</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="3">
         <v>46083</v>
       </c>
@@ -551,7 +1036,7 @@
         <v>11</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D3" s="1">
         <v>50</v>
@@ -560,32 +1045,32 @@
         <v>12</v>
       </c>
       <c r="F3" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="F3:F5" si="0">(D3*E3)</f>
         <v>600</v>
       </c>
       <c r="G3" s="1">
-        <f t="shared" ref="G3:G30" si="2">IF(C3="Compra", G2+D3, G2-D3)</f>
+        <f>IF(C3="Compra", G2+D3, G2-D3)</f>
         <v>150</v>
       </c>
       <c r="H3" s="2">
-        <f t="shared" ref="H3:H30" si="3">IF(C3="Compra", (I2+F3)/(G2+D3), H2)</f>
+        <f>IF(C3="Compra", (I2+F3)/(G2+D3), H2)</f>
         <v>10.666666666666666</v>
       </c>
       <c r="I3" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="I3:I5" si="1">G3*H3</f>
         <v>1600</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
-        <f t="shared" ref="A4:A30" si="4">A3+1</f>
+        <f>A3+1</f>
         <v>46084</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>12</v>
       </c>
       <c r="D4" s="1">
         <v>30</v>
@@ -598,11 +1083,11 @@
         <v>450</v>
       </c>
       <c r="G4" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="G4" si="2">IF(C4="Compra", G3+D4, G3-D4)</f>
         <v>120</v>
       </c>
       <c r="H4" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="H4:H5" si="3">IF(C4="Compra", (I3+F4)/(G3+D4), H3)</f>
         <v>10.666666666666666</v>
       </c>
       <c r="I4" s="2">
@@ -610,16 +1095,16 @@
         <v>1280</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="A5:A30" si="4">A4+1</f>
         <v>46085</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D5" s="1">
         <v>80</v>
@@ -632,7 +1117,7 @@
         <v>880</v>
       </c>
       <c r="G5" s="1">
-        <f t="shared" si="2"/>
+        <f>IF(C5="Compra", G4+D5, G4-D5)</f>
         <v>200</v>
       </c>
       <c r="H5" s="2">
@@ -644,16 +1129,16 @@
         <v>2160</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="3">
         <f t="shared" si="4"/>
         <v>46086</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D6" s="1">
         <v>100</v>
@@ -662,32 +1147,32 @@
         <v>11</v>
       </c>
       <c r="F6" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="F6:F30" si="5">(D6*E6)</f>
         <v>1100</v>
       </c>
       <c r="G6" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="G6:G30" si="6">IF(C6="Compra", G5+D6, G5-D6)</f>
         <v>300</v>
       </c>
       <c r="H6" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="H6:H30" si="7">IF(C6="Compra", (I5+F6)/(G5+D6), H5)</f>
         <v>10.866666666666667</v>
       </c>
       <c r="I6" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="I6:I30" si="8">G6*H6</f>
         <v>3260</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="3">
         <f t="shared" si="4"/>
         <v>46087</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D7" s="1">
         <v>50</v>
@@ -696,32 +1181,32 @@
         <v>12</v>
       </c>
       <c r="F7" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>600</v>
       </c>
       <c r="G7" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>350</v>
       </c>
       <c r="H7" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>11.028571428571428</v>
       </c>
       <c r="I7" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="8"/>
         <v>3860</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="3">
         <f t="shared" si="4"/>
         <v>46088</v>
       </c>
       <c r="B8" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>12</v>
       </c>
       <c r="D8" s="1">
         <v>100</v>
@@ -730,32 +1215,32 @@
         <v>15</v>
       </c>
       <c r="F8" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>1500</v>
       </c>
       <c r="G8" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>250</v>
       </c>
       <c r="H8" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>11.028571428571428</v>
       </c>
       <c r="I8" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="8"/>
         <v>2757.1428571428573</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="3">
         <f t="shared" si="4"/>
         <v>46089</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D9" s="1">
         <v>20</v>
@@ -764,32 +1249,32 @@
         <v>15</v>
       </c>
       <c r="F9" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>300</v>
       </c>
       <c r="G9" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>230</v>
       </c>
       <c r="H9" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>11.028571428571428</v>
       </c>
       <c r="I9" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="8"/>
         <v>2536.5714285714284</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" s="3">
         <f t="shared" si="4"/>
         <v>46090</v>
       </c>
       <c r="B10" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>12</v>
       </c>
       <c r="D10" s="1">
         <v>50</v>
@@ -798,23 +1283,23 @@
         <v>15</v>
       </c>
       <c r="F10" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>750</v>
       </c>
       <c r="G10" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>180</v>
       </c>
       <c r="H10" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>11.028571428571428</v>
       </c>
       <c r="I10" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="8"/>
         <v>1985.1428571428571</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="3">
         <f t="shared" si="4"/>
         <v>46091</v>
@@ -823,7 +1308,7 @@
         <v>11</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D11" s="1">
         <v>100</v>
@@ -832,32 +1317,32 @@
         <v>13</v>
       </c>
       <c r="F11" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>1300</v>
       </c>
       <c r="G11" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>280</v>
       </c>
       <c r="H11" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>11.732653061224489</v>
       </c>
       <c r="I11" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="8"/>
         <v>3285.1428571428569</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="3">
         <f t="shared" si="4"/>
         <v>46092</v>
       </c>
       <c r="B12" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>12</v>
       </c>
       <c r="D12" s="1">
         <v>50</v>
@@ -866,32 +1351,32 @@
         <v>15</v>
       </c>
       <c r="F12" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>750</v>
       </c>
       <c r="G12" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>230</v>
       </c>
       <c r="H12" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>11.732653061224489</v>
       </c>
       <c r="I12" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="8"/>
         <v>2698.5102040816328</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="3">
         <f t="shared" si="4"/>
         <v>46093</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D13" s="1">
         <v>200</v>
@@ -900,32 +1385,32 @@
         <v>13</v>
       </c>
       <c r="F13" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>2600</v>
       </c>
       <c r="G13" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>430</v>
       </c>
       <c r="H13" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>12.322116753678216</v>
       </c>
       <c r="I13" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="8"/>
         <v>5298.5102040816328</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" s="3">
         <f t="shared" si="4"/>
         <v>46094</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D14" s="1">
         <v>100</v>
@@ -934,23 +1419,23 @@
         <v>13</v>
       </c>
       <c r="F14" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>1300</v>
       </c>
       <c r="G14" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>530</v>
       </c>
       <c r="H14" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>12.450019252984212</v>
       </c>
       <c r="I14" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="8"/>
         <v>6598.5102040816328</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" s="3">
         <f t="shared" si="4"/>
         <v>46095</v>
@@ -959,7 +1444,7 @@
         <v>11</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D15" s="1">
         <v>300</v>
@@ -968,32 +1453,32 @@
         <v>15</v>
       </c>
       <c r="F15" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>4500</v>
       </c>
       <c r="G15" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>230</v>
       </c>
       <c r="H15" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>12.450019252984212</v>
       </c>
       <c r="I15" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="8"/>
         <v>2863.5044281863688</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" s="3">
         <f t="shared" si="4"/>
         <v>46096</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D16" s="1">
         <v>200</v>
@@ -1002,32 +1487,32 @@
         <v>14</v>
       </c>
       <c r="F16" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>2800</v>
       </c>
       <c r="G16" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>430</v>
       </c>
       <c r="H16" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>13.170940530665973</v>
       </c>
       <c r="I16" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="8"/>
         <v>5663.5044281863684</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" s="3">
         <f t="shared" si="4"/>
         <v>46097</v>
       </c>
       <c r="B17" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C17" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>12</v>
       </c>
       <c r="D17" s="1">
         <v>100</v>
@@ -1036,32 +1521,32 @@
         <v>16</v>
       </c>
       <c r="F17" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>1600</v>
       </c>
       <c r="G17" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>330</v>
       </c>
       <c r="H17" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>13.170940530665973</v>
       </c>
       <c r="I17" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="8"/>
         <v>4346.4103751197708</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" s="3">
         <f t="shared" si="4"/>
         <v>46098</v>
       </c>
       <c r="B18" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C18" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>12</v>
       </c>
       <c r="D18" s="1">
         <v>200</v>
@@ -1070,32 +1555,32 @@
         <v>17</v>
       </c>
       <c r="F18" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>3400</v>
       </c>
       <c r="G18" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>130</v>
       </c>
       <c r="H18" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>13.170940530665973</v>
       </c>
       <c r="I18" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="8"/>
         <v>1712.2222689865766</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" s="3">
         <f t="shared" si="4"/>
         <v>46099</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D19" s="1">
         <v>50</v>
@@ -1104,32 +1589,32 @@
         <v>16</v>
       </c>
       <c r="F19" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>800</v>
       </c>
       <c r="G19" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>80</v>
       </c>
       <c r="H19" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>13.170940530665973</v>
       </c>
       <c r="I19" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="8"/>
         <v>1053.6752424532779</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" s="3">
         <f t="shared" si="4"/>
         <v>46100</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D20" s="1">
         <v>200</v>
@@ -1138,32 +1623,32 @@
         <v>18</v>
       </c>
       <c r="F20" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>3600</v>
       </c>
       <c r="G20" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>280</v>
       </c>
       <c r="H20" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>16.62026872304742</v>
       </c>
       <c r="I20" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="8"/>
         <v>4653.6752424532779</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" s="3">
         <f t="shared" si="4"/>
         <v>46101</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D21" s="1">
         <v>100</v>
@@ -1172,32 +1657,32 @@
         <v>23</v>
       </c>
       <c r="F21" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>2300</v>
       </c>
       <c r="G21" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>180</v>
       </c>
       <c r="H21" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>16.62026872304742</v>
       </c>
       <c r="I21" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="8"/>
         <v>2991.6483701485358</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" s="3">
         <f t="shared" si="4"/>
         <v>46102</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D22" s="1">
         <v>200</v>
@@ -1206,32 +1691,32 @@
         <v>16</v>
       </c>
       <c r="F22" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>3200</v>
       </c>
       <c r="G22" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>380</v>
       </c>
       <c r="H22" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>16.293811500390884</v>
       </c>
       <c r="I22" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="8"/>
         <v>6191.6483701485358</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" s="3">
         <f t="shared" si="4"/>
         <v>46103</v>
       </c>
       <c r="B23" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C23" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>12</v>
       </c>
       <c r="D23" s="1">
         <v>300</v>
@@ -1240,32 +1725,32 @@
         <v>20</v>
       </c>
       <c r="F23" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>6000</v>
       </c>
       <c r="G23" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>80</v>
       </c>
       <c r="H23" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>16.293811500390884</v>
       </c>
       <c r="I23" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="8"/>
         <v>1303.5049200312708</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" s="3">
         <f t="shared" si="4"/>
         <v>46104</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D24" s="1">
         <v>20</v>
@@ -1274,23 +1759,23 @@
         <v>18</v>
       </c>
       <c r="F24" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>360</v>
       </c>
       <c r="G24" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>100</v>
       </c>
       <c r="H24" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>16.635049200312707</v>
       </c>
       <c r="I24" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="8"/>
         <v>1663.5049200312708</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" s="3">
         <f t="shared" si="4"/>
         <v>46105</v>
@@ -1299,7 +1784,7 @@
         <v>11</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D25" s="1">
         <v>500</v>
@@ -1308,32 +1793,32 @@
         <v>15</v>
       </c>
       <c r="F25" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>7500</v>
       </c>
       <c r="G25" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>600</v>
       </c>
       <c r="H25" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>15.272508200052119</v>
       </c>
       <c r="I25" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="8"/>
         <v>9163.5049200312715</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" s="3">
         <f t="shared" si="4"/>
         <v>46106</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D26" s="1">
         <v>100</v>
@@ -1342,32 +1827,32 @@
         <v>16</v>
       </c>
       <c r="F26" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>1600</v>
       </c>
       <c r="G26" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>700</v>
       </c>
       <c r="H26" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>15.376435600044674</v>
       </c>
       <c r="I26" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="8"/>
         <v>10763.504920031271</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" s="3">
         <f t="shared" si="4"/>
         <v>46107</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D27" s="1">
         <v>200</v>
@@ -1376,32 +1861,32 @@
         <v>17</v>
       </c>
       <c r="F27" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>3400</v>
       </c>
       <c r="G27" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>900</v>
       </c>
       <c r="H27" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>15.737227688923635</v>
       </c>
       <c r="I27" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="8"/>
         <v>14163.504920031271</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" s="3">
         <f t="shared" si="4"/>
         <v>46108</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D28" s="1">
         <v>500</v>
@@ -1410,32 +1895,32 @@
         <v>20</v>
       </c>
       <c r="F28" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>10000</v>
       </c>
       <c r="G28" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>1400</v>
       </c>
       <c r="H28" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>17.259646371450909</v>
       </c>
       <c r="I28" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="8"/>
         <v>24163.504920031271</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" s="3">
         <f t="shared" si="4"/>
         <v>46109</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D29" s="1">
         <v>100</v>
@@ -1444,32 +1929,32 @@
         <v>16</v>
       </c>
       <c r="F29" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>1600</v>
       </c>
       <c r="G29" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>1500</v>
       </c>
       <c r="H29" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>17.175669946687513</v>
       </c>
       <c r="I29" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="8"/>
         <v>25763.504920031271</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" s="3">
         <f t="shared" si="4"/>
         <v>46110</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D30" s="1">
         <v>300</v>
@@ -1478,29 +1963,24 @@
         <v>18</v>
       </c>
       <c r="F30" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>5400</v>
       </c>
       <c r="G30" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>1800</v>
       </c>
       <c r="H30" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>17.313058288906262</v>
       </c>
       <c r="I30" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="8"/>
         <v>31163.504920031271</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="E31" s="1"/>
-      <c r="F31" s="1"/>
-      <c r="H31" s="1"/>
-      <c r="I31" s="1"/>
-    </row>
   </sheetData>
+  <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/TabelaEstoque.xlsx
+++ b/TabelaEstoque.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marcel\Desktop\Nova pasta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02F4420A-2289-42BB-A57A-DBEAD8AB5F45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{094B85A9-817B-469F-9374-88F426D0DCF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="17">
   <si>
     <t>Data</t>
   </si>
@@ -31,6 +31,9 @@
     <t>Tipo</t>
   </si>
   <si>
+    <t>Cliente/Fornecedor</t>
+  </si>
+  <si>
     <t>Quantidade</t>
   </si>
   <si>
@@ -64,7 +67,10 @@
     <t>Tomate</t>
   </si>
   <si>
-    <t>Cliente/Fornecedor</t>
+    <t>Fornecedor</t>
+  </si>
+  <si>
+    <t>Cliente</t>
   </si>
 </sst>
 </file>
@@ -74,7 +80,7 @@
   <numFmts count="1">
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -86,14 +92,6 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -131,13 +129,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -453,29 +450,29 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
-        <v>14</v>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
@@ -483,10 +480,13 @@
         <v>46085</v>
       </c>
       <c r="B2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C2" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="D2" t="s">
+        <v>15</v>
       </c>
       <c r="E2">
         <v>80</v>
@@ -515,10 +515,13 @@
         <v>46087</v>
       </c>
       <c r="B3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C3" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="D3" t="s">
+        <v>15</v>
       </c>
       <c r="E3">
         <v>50</v>
@@ -547,10 +550,13 @@
         <v>46088</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C4" t="s">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="D4" t="s">
+        <v>16</v>
       </c>
       <c r="E4">
         <v>100</v>
@@ -579,10 +585,13 @@
         <v>46089</v>
       </c>
       <c r="B5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C5" t="s">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="D5" t="s">
+        <v>16</v>
       </c>
       <c r="E5">
         <v>20</v>
@@ -611,10 +620,13 @@
         <v>46092</v>
       </c>
       <c r="B6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C6" t="s">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="D6" t="s">
+        <v>16</v>
       </c>
       <c r="E6">
         <v>50</v>
@@ -643,10 +655,13 @@
         <v>46093</v>
       </c>
       <c r="B7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C7" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="D7" t="s">
+        <v>15</v>
       </c>
       <c r="E7">
         <v>200</v>
@@ -675,10 +690,13 @@
         <v>46094</v>
       </c>
       <c r="B8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C8" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="D8" t="s">
+        <v>15</v>
       </c>
       <c r="E8">
         <v>100</v>
@@ -707,10 +725,13 @@
         <v>46098</v>
       </c>
       <c r="B9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C9" t="s">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="D9" t="s">
+        <v>16</v>
       </c>
       <c r="E9">
         <v>200</v>
@@ -739,10 +760,13 @@
         <v>46099</v>
       </c>
       <c r="B10" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C10" t="s">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="D10" t="s">
+        <v>16</v>
       </c>
       <c r="E10">
         <v>50</v>
@@ -771,10 +795,13 @@
         <v>46100</v>
       </c>
       <c r="B11" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C11" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="D11" t="s">
+        <v>15</v>
       </c>
       <c r="E11">
         <v>200</v>
@@ -803,10 +830,13 @@
         <v>46101</v>
       </c>
       <c r="B12" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C12" t="s">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="D12" t="s">
+        <v>16</v>
       </c>
       <c r="E12">
         <v>100</v>
@@ -835,10 +865,13 @@
         <v>46102</v>
       </c>
       <c r="B13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C13" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="D13" t="s">
+        <v>15</v>
       </c>
       <c r="E13">
         <v>200</v>
@@ -867,10 +900,13 @@
         <v>46103</v>
       </c>
       <c r="B14" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C14" t="s">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="D14" t="s">
+        <v>16</v>
       </c>
       <c r="E14">
         <v>300</v>
@@ -899,10 +935,13 @@
         <v>46104</v>
       </c>
       <c r="B15" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C15" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="D15" t="s">
+        <v>15</v>
       </c>
       <c r="E15">
         <v>20</v>
@@ -931,10 +970,13 @@
         <v>46106</v>
       </c>
       <c r="B16" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C16" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="D16" t="s">
+        <v>15</v>
       </c>
       <c r="E16">
         <v>100</v>
@@ -963,10 +1005,13 @@
         <v>46107</v>
       </c>
       <c r="B17" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C17" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="D17" t="s">
+        <v>15</v>
       </c>
       <c r="E17">
         <v>200</v>
@@ -995,10 +1040,13 @@
         <v>46108</v>
       </c>
       <c r="B18" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C18" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="D18" t="s">
+        <v>15</v>
       </c>
       <c r="E18">
         <v>500</v>
@@ -1027,10 +1075,13 @@
         <v>46109</v>
       </c>
       <c r="B19" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C19" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="D19" t="s">
+        <v>15</v>
       </c>
       <c r="E19">
         <v>100</v>
@@ -1059,10 +1110,13 @@
         <v>46082</v>
       </c>
       <c r="B20" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C20" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="D20" t="s">
+        <v>15</v>
       </c>
       <c r="E20">
         <v>100</v>
@@ -1091,10 +1145,13 @@
         <v>46083</v>
       </c>
       <c r="B21" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C21" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="D21" t="s">
+        <v>15</v>
       </c>
       <c r="E21">
         <v>50</v>
@@ -1123,10 +1180,13 @@
         <v>46084</v>
       </c>
       <c r="B22" t="s">
+        <v>14</v>
+      </c>
+      <c r="C22" t="s">
         <v>13</v>
       </c>
-      <c r="C22" t="s">
-        <v>12</v>
+      <c r="D22" t="s">
+        <v>16</v>
       </c>
       <c r="E22">
         <v>30</v>
@@ -1155,10 +1215,13 @@
         <v>46086</v>
       </c>
       <c r="B23" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C23" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="D23" t="s">
+        <v>15</v>
       </c>
       <c r="E23">
         <v>100</v>
@@ -1187,10 +1250,13 @@
         <v>46090</v>
       </c>
       <c r="B24" t="s">
+        <v>14</v>
+      </c>
+      <c r="C24" t="s">
         <v>13</v>
       </c>
-      <c r="C24" t="s">
-        <v>12</v>
+      <c r="D24" t="s">
+        <v>16</v>
       </c>
       <c r="E24">
         <v>50</v>
@@ -1219,10 +1285,13 @@
         <v>46091</v>
       </c>
       <c r="B25" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C25" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="D25" t="s">
+        <v>15</v>
       </c>
       <c r="E25">
         <v>100</v>
@@ -1251,10 +1320,13 @@
         <v>46095</v>
       </c>
       <c r="B26" t="s">
+        <v>14</v>
+      </c>
+      <c r="C26" t="s">
         <v>13</v>
       </c>
-      <c r="C26" t="s">
-        <v>12</v>
+      <c r="D26" t="s">
+        <v>16</v>
       </c>
       <c r="E26">
         <v>300</v>
@@ -1283,10 +1355,13 @@
         <v>46096</v>
       </c>
       <c r="B27" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C27" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="D27" t="s">
+        <v>15</v>
       </c>
       <c r="E27">
         <v>200</v>
@@ -1315,10 +1390,13 @@
         <v>46097</v>
       </c>
       <c r="B28" t="s">
+        <v>14</v>
+      </c>
+      <c r="C28" t="s">
         <v>13</v>
       </c>
-      <c r="C28" t="s">
-        <v>12</v>
+      <c r="D28" t="s">
+        <v>16</v>
       </c>
       <c r="E28">
         <v>100</v>
@@ -1347,10 +1425,13 @@
         <v>46105</v>
       </c>
       <c r="B29" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C29" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="D29" t="s">
+        <v>15</v>
       </c>
       <c r="E29">
         <v>500</v>
@@ -1379,10 +1460,13 @@
         <v>46110</v>
       </c>
       <c r="B30" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C30" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="D30" t="s">
+        <v>15</v>
       </c>
       <c r="E30">
         <v>300</v>

--- a/TabelaEstoque.xlsx
+++ b/TabelaEstoque.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marcel\Desktop\Nova pasta\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Outros computadores\Meu laptop\Nova pasta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{094B85A9-817B-469F-9374-88F426D0DCF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CCF795B-D5B1-4CB7-A600-A1282201228B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="31">
   <si>
     <t>Data</t>
   </si>
@@ -67,10 +67,52 @@
     <t>Tomate</t>
   </si>
   <si>
-    <t>Fornecedor</t>
-  </si>
-  <si>
-    <t>Cliente</t>
+    <t>Forma Pagamento</t>
+  </si>
+  <si>
+    <t>Parcelas</t>
+  </si>
+  <si>
+    <t>Data Recebimento</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Mercado Central</t>
+  </si>
+  <si>
+    <t>Padaria do João</t>
+  </si>
+  <si>
+    <t>Quitanda da Maria</t>
+  </si>
+  <si>
+    <t>Restaurante Saboroso</t>
+  </si>
+  <si>
+    <t>Fazenda São José</t>
+  </si>
+  <si>
+    <t>Distribuidora Nacional</t>
+  </si>
+  <si>
+    <t>Atacadão das Frutas</t>
+  </si>
+  <si>
+    <t>À Vista</t>
+  </si>
+  <si>
+    <t>A Prazo</t>
+  </si>
+  <si>
+    <t>Pago</t>
+  </si>
+  <si>
+    <t>Pendente</t>
+  </si>
+  <si>
+    <t>Recebido</t>
   </si>
 </sst>
 </file>
@@ -78,9 +120,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -92,6 +134,14 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -129,12 +179,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -437,10 +489,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K30"/>
+  <dimension ref="A1:O30"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="17.5703125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -474,8 +530,20 @@
       <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L1" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="N1" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="O1" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>46085</v>
       </c>
@@ -486,7 +554,7 @@
         <v>12</v>
       </c>
       <c r="D2" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="E2">
         <v>80</v>
@@ -509,8 +577,20 @@
       <c r="K2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L2" t="s">
+        <v>26</v>
+      </c>
+      <c r="M2">
+        <v>1</v>
+      </c>
+      <c r="N2" s="4">
+        <v>46085</v>
+      </c>
+      <c r="O2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>46087</v>
       </c>
@@ -521,7 +601,7 @@
         <v>12</v>
       </c>
       <c r="D3" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="E3">
         <v>50</v>
@@ -544,8 +624,20 @@
       <c r="K3">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L3" t="s">
+        <v>26</v>
+      </c>
+      <c r="M3">
+        <v>1</v>
+      </c>
+      <c r="N3" s="4">
+        <v>46085</v>
+      </c>
+      <c r="O3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>46088</v>
       </c>
@@ -556,7 +648,7 @@
         <v>13</v>
       </c>
       <c r="D4" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E4">
         <v>100</v>
@@ -577,10 +669,22 @@
         <v>341.53846153846149</v>
       </c>
       <c r="K4">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+      <c r="L4" t="s">
+        <v>26</v>
+      </c>
+      <c r="M4">
+        <v>1</v>
+      </c>
+      <c r="N4" s="4">
+        <v>46085</v>
+      </c>
+      <c r="O4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>46089</v>
       </c>
@@ -591,7 +695,7 @@
         <v>13</v>
       </c>
       <c r="D5" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="E5">
         <v>20</v>
@@ -612,10 +716,22 @@
         <v>113.8461538461539</v>
       </c>
       <c r="K5">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+      <c r="L5" t="s">
+        <v>26</v>
+      </c>
+      <c r="M5">
+        <v>1</v>
+      </c>
+      <c r="N5" s="4">
+        <v>46120</v>
+      </c>
+      <c r="O5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>46092</v>
       </c>
@@ -626,7 +742,7 @@
         <v>13</v>
       </c>
       <c r="D6" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E6">
         <v>50</v>
@@ -647,10 +763,22 @@
         <v>-455.38461538461542</v>
       </c>
       <c r="K6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+      <c r="L6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M6">
+        <v>1</v>
+      </c>
+      <c r="N6" s="4">
+        <v>46118</v>
+      </c>
+      <c r="O6" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>46093</v>
       </c>
@@ -661,7 +789,7 @@
         <v>12</v>
       </c>
       <c r="D7" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="E7">
         <v>200</v>
@@ -682,10 +810,22 @@
         <v>2144.6153846153852</v>
       </c>
       <c r="K7">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+      <c r="L7" t="s">
+        <v>27</v>
+      </c>
+      <c r="M7">
+        <v>2</v>
+      </c>
+      <c r="N7" s="4">
+        <v>46085</v>
+      </c>
+      <c r="O7" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>46094</v>
       </c>
@@ -696,7 +836,7 @@
         <v>12</v>
       </c>
       <c r="D8" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="E8">
         <v>100</v>
@@ -717,10 +857,22 @@
         <v>3444.6153846153852</v>
       </c>
       <c r="K8">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+      <c r="L8" t="s">
+        <v>27</v>
+      </c>
+      <c r="M8">
+        <v>2</v>
+      </c>
+      <c r="N8" s="4">
+        <v>46085</v>
+      </c>
+      <c r="O8" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>46098</v>
       </c>
@@ -731,7 +883,7 @@
         <v>13</v>
       </c>
       <c r="D9" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="E9">
         <v>200</v>
@@ -752,10 +904,22 @@
         <v>794.91124260355025</v>
       </c>
       <c r="K9">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+      <c r="L9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M9">
+        <v>1</v>
+      </c>
+      <c r="N9" s="4">
+        <v>46120</v>
+      </c>
+      <c r="O9" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>46099</v>
       </c>
@@ -766,7 +930,7 @@
         <v>13</v>
       </c>
       <c r="D10" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E10">
         <v>50</v>
@@ -787,10 +951,22 @@
         <v>132.48520710059171</v>
       </c>
       <c r="K10">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="L10" t="s">
+        <v>27</v>
+      </c>
+      <c r="M10">
+        <v>2</v>
+      </c>
+      <c r="N10" s="4">
+        <v>46120</v>
+      </c>
+      <c r="O10" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>46100</v>
       </c>
@@ -801,7 +977,7 @@
         <v>12</v>
       </c>
       <c r="D11" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="E11">
         <v>200</v>
@@ -822,10 +998,22 @@
         <v>3732.4852071005921</v>
       </c>
       <c r="K11">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+      <c r="L11" t="s">
+        <v>27</v>
+      </c>
+      <c r="M11">
+        <v>2</v>
+      </c>
+      <c r="N11" s="4">
+        <v>46118</v>
+      </c>
+      <c r="O11" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>46101</v>
       </c>
@@ -836,7 +1024,7 @@
         <v>13</v>
       </c>
       <c r="D12" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="E12">
         <v>100</v>
@@ -857,10 +1045,22 @@
         <v>1955.1112989574531</v>
       </c>
       <c r="K12">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="L12" t="s">
+        <v>27</v>
+      </c>
+      <c r="M12">
+        <v>2</v>
+      </c>
+      <c r="N12" s="4">
+        <v>46118</v>
+      </c>
+      <c r="O12" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>46102</v>
       </c>
@@ -871,7 +1071,7 @@
         <v>12</v>
       </c>
       <c r="D13" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="E13">
         <v>200</v>
@@ -892,10 +1092,22 @@
         <v>5155.1112989574531</v>
       </c>
       <c r="K13">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+      <c r="L13" t="s">
+        <v>26</v>
+      </c>
+      <c r="M13">
+        <v>1</v>
+      </c>
+      <c r="N13" s="4">
+        <v>46085</v>
+      </c>
+      <c r="O13" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>46103</v>
       </c>
@@ -906,7 +1118,7 @@
         <v>13</v>
       </c>
       <c r="D14" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E14">
         <v>300</v>
@@ -927,10 +1139,22 @@
         <v>166.29391286959529</v>
       </c>
       <c r="K14">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+      <c r="L14" t="s">
+        <v>26</v>
+      </c>
+      <c r="M14">
+        <v>1</v>
+      </c>
+      <c r="N14" s="4">
+        <v>46085</v>
+      </c>
+      <c r="O14" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>46104</v>
       </c>
@@ -941,7 +1165,7 @@
         <v>12</v>
       </c>
       <c r="D15" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="E15">
         <v>20</v>
@@ -962,10 +1186,22 @@
         <v>526.29391286959526</v>
       </c>
       <c r="K15">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+      <c r="L15" t="s">
+        <v>26</v>
+      </c>
+      <c r="M15">
+        <v>1</v>
+      </c>
+      <c r="N15" s="4">
+        <v>46120</v>
+      </c>
+      <c r="O15" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>46106</v>
       </c>
@@ -976,7 +1212,7 @@
         <v>12</v>
       </c>
       <c r="D16" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="E16">
         <v>100</v>
@@ -997,10 +1233,22 @@
         <v>2126.2939128695948</v>
       </c>
       <c r="K16">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+      <c r="L16" t="s">
+        <v>27</v>
+      </c>
+      <c r="M16">
+        <v>2</v>
+      </c>
+      <c r="N16" s="4">
+        <v>46120</v>
+      </c>
+      <c r="O16" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>46107</v>
       </c>
@@ -1011,7 +1259,7 @@
         <v>12</v>
       </c>
       <c r="D17" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="E17">
         <v>200</v>
@@ -1032,10 +1280,22 @@
         <v>5526.2939128695953</v>
       </c>
       <c r="K17">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+      <c r="L17" t="s">
+        <v>27</v>
+      </c>
+      <c r="M17">
+        <v>2</v>
+      </c>
+      <c r="N17" s="4">
+        <v>46118</v>
+      </c>
+      <c r="O17" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>46108</v>
       </c>
@@ -1046,7 +1306,7 @@
         <v>12</v>
       </c>
       <c r="D18" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="E18">
         <v>500</v>
@@ -1067,10 +1327,22 @@
         <v>15526.293912869591</v>
       </c>
       <c r="K18">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="L18" t="s">
+        <v>27</v>
+      </c>
+      <c r="M18">
+        <v>2</v>
+      </c>
+      <c r="N18" s="4">
+        <v>46085</v>
+      </c>
+      <c r="O18" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>46109</v>
       </c>
@@ -1081,7 +1353,7 @@
         <v>12</v>
       </c>
       <c r="D19" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="E19">
         <v>100</v>
@@ -1102,10 +1374,22 @@
         <v>17126.293912869591</v>
       </c>
       <c r="K19">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="L19" t="s">
+        <v>26</v>
+      </c>
+      <c r="M19">
+        <v>1</v>
+      </c>
+      <c r="N19" s="4">
+        <v>46085</v>
+      </c>
+      <c r="O19" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>46082</v>
       </c>
@@ -1116,7 +1400,7 @@
         <v>12</v>
       </c>
       <c r="D20" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="E20">
         <v>100</v>
@@ -1139,8 +1423,20 @@
       <c r="K20">
         <v>19</v>
       </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L20" t="s">
+        <v>26</v>
+      </c>
+      <c r="M20">
+        <v>1</v>
+      </c>
+      <c r="N20" s="4">
+        <v>46085</v>
+      </c>
+      <c r="O20" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>46083</v>
       </c>
@@ -1151,7 +1447,7 @@
         <v>12</v>
       </c>
       <c r="D21" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="E21">
         <v>50</v>
@@ -1174,8 +1470,20 @@
       <c r="K21">
         <v>20</v>
       </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L21" t="s">
+        <v>27</v>
+      </c>
+      <c r="M21">
+        <v>2</v>
+      </c>
+      <c r="N21" s="4">
+        <v>46120</v>
+      </c>
+      <c r="O21" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>46084</v>
       </c>
@@ -1186,7 +1494,7 @@
         <v>13</v>
       </c>
       <c r="D22" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E22">
         <v>30</v>
@@ -1209,8 +1517,20 @@
       <c r="K22">
         <v>21</v>
       </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L22" t="s">
+        <v>27</v>
+      </c>
+      <c r="M22">
+        <v>2</v>
+      </c>
+      <c r="N22" s="4">
+        <v>46118</v>
+      </c>
+      <c r="O22" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>46086</v>
       </c>
@@ -1221,7 +1541,7 @@
         <v>12</v>
       </c>
       <c r="D23" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="E23">
         <v>100</v>
@@ -1244,8 +1564,20 @@
       <c r="K23">
         <v>22</v>
       </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L23" t="s">
+        <v>27</v>
+      </c>
+      <c r="M23">
+        <v>2</v>
+      </c>
+      <c r="N23" s="4">
+        <v>46118</v>
+      </c>
+      <c r="O23" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>46090</v>
       </c>
@@ -1256,7 +1588,7 @@
         <v>13</v>
       </c>
       <c r="D24" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E24">
         <v>50</v>
@@ -1279,8 +1611,20 @@
       <c r="K24">
         <v>23</v>
       </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L24" t="s">
+        <v>27</v>
+      </c>
+      <c r="M24">
+        <v>2</v>
+      </c>
+      <c r="N24" s="4">
+        <v>46085</v>
+      </c>
+      <c r="O24" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>46091</v>
       </c>
@@ -1291,7 +1635,7 @@
         <v>12</v>
       </c>
       <c r="D25" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="E25">
         <v>100</v>
@@ -1314,8 +1658,20 @@
       <c r="K25">
         <v>24</v>
       </c>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L25" t="s">
+        <v>27</v>
+      </c>
+      <c r="M25">
+        <v>2</v>
+      </c>
+      <c r="N25" s="4">
+        <v>46085</v>
+      </c>
+      <c r="O25" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>46095</v>
       </c>
@@ -1326,7 +1682,7 @@
         <v>13</v>
       </c>
       <c r="D26" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="E26">
         <v>300</v>
@@ -1349,8 +1705,20 @@
       <c r="K26">
         <v>25</v>
       </c>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L26" t="s">
+        <v>26</v>
+      </c>
+      <c r="M26">
+        <v>1</v>
+      </c>
+      <c r="N26" s="4">
+        <v>46085</v>
+      </c>
+      <c r="O26" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <v>46096</v>
       </c>
@@ -1361,7 +1729,7 @@
         <v>12</v>
       </c>
       <c r="D27" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="E27">
         <v>200</v>
@@ -1384,8 +1752,20 @@
       <c r="K27">
         <v>26</v>
       </c>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L27" t="s">
+        <v>26</v>
+      </c>
+      <c r="M27">
+        <v>1</v>
+      </c>
+      <c r="N27" s="4">
+        <v>46118</v>
+      </c>
+      <c r="O27" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <v>46097</v>
       </c>
@@ -1396,7 +1776,7 @@
         <v>13</v>
       </c>
       <c r="D28" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="E28">
         <v>100</v>
@@ -1419,8 +1799,20 @@
       <c r="K28">
         <v>27</v>
       </c>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L28" t="s">
+        <v>27</v>
+      </c>
+      <c r="M28">
+        <v>2</v>
+      </c>
+      <c r="N28" s="4">
+        <v>46118</v>
+      </c>
+      <c r="O28" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <v>46105</v>
       </c>
@@ -1431,7 +1823,7 @@
         <v>12</v>
       </c>
       <c r="D29" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="E29">
         <v>500</v>
@@ -1454,8 +1846,20 @@
       <c r="K29">
         <v>28</v>
       </c>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L29" t="s">
+        <v>27</v>
+      </c>
+      <c r="M29">
+        <v>2</v>
+      </c>
+      <c r="N29" s="4">
+        <v>46085</v>
+      </c>
+      <c r="O29" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <v>46110</v>
       </c>
@@ -1466,7 +1870,7 @@
         <v>12</v>
       </c>
       <c r="D30" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="E30">
         <v>300</v>
@@ -1489,8 +1893,21 @@
       <c r="K30">
         <v>29</v>
       </c>
+      <c r="L30" t="s">
+        <v>26</v>
+      </c>
+      <c r="M30">
+        <v>1</v>
+      </c>
+      <c r="N30" s="4">
+        <v>46085</v>
+      </c>
+      <c r="O30" t="s">
+        <v>28</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/TabelaEstoque.xlsx
+++ b/TabelaEstoque.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O1"/>
+  <dimension ref="A1:T1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -502,6 +502,31 @@
       <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Status</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Motivo Perda</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Parcela</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Parcelas Pagas</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Valor Pago</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Valor Restante</t>
         </is>
       </c>
     </row>
